--- a/SGC-CKN/Excel/43c21782-c48f-47d0-9408-3f013a3267be_Thị_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-100_D800_05-04-2026.xlsx
+++ b/SGC-CKN/Excel/43c21782-c48f-47d0-9408-3f013a3267be_Thị_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-100_D800_05-04-2026.xlsx
@@ -95,51 +95,51 @@
     <t>Đất thổ nhưỡng</t>
   </si>
   <si>
+    <t xml:space="preserve">11:00
+05/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:10
+05/04/2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:30
+05/04/2026</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:45
+05/04/2026</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Sét xám trắng, xám xanh dẻo chảy</t>
+  </si>
+  <si>
     <t xml:space="preserve">14:00
 05/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">14:10
-05/04/2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:50
-05/04/2026</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00
-05/04/2026</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:45
-05/04/2026</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">14:40
@@ -149,7 +149,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">15:30
@@ -159,7 +159,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">16:40
@@ -169,7 +169,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">18:15
@@ -332,17 +332,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFECACA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -493,26 +493,26 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1183,85 +1183,85 @@
         <v>-5</v>
       </c>
       <c r="H12" s="9">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="I12" s="9">
         <v>3.3</v>
       </c>
-      <c r="J12" s="12">
-        <v>4.95</v>
+      <c r="J12" s="8">
+        <v>9.9</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>-5</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>-8</v>
       </c>
-      <c r="H13" s="13">
-        <v>0.17</v>
-      </c>
-      <c r="I13" s="13">
+      <c r="H13" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="I13" s="12">
         <v>3</v>
       </c>
       <c r="J13" s="8">
-        <v>18</v>
-      </c>
-      <c r="K13" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>-8</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="15">
         <v>-17</v>
       </c>
-      <c r="H14" s="16">
-        <v>0.25</v>
-      </c>
-      <c r="I14" s="16">
+      <c r="H14" s="15">
+        <v>2.25</v>
+      </c>
+      <c r="I14" s="15">
         <v>9</v>
       </c>
-      <c r="J14" s="8">
-        <v>36</v>
-      </c>
-      <c r="K14" s="17" t="s">
+      <c r="J14" s="18">
+        <v>4</v>
+      </c>
+      <c r="K14" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
         <v>40</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E15" s="21" t="s">
         <v>41</v>
@@ -1328,7 +1328,7 @@
       <c r="I16" s="22">
         <v>4</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="18">
         <v>4.8</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -1398,7 +1398,7 @@
       <c r="I18" s="28">
         <v>4.72</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="18">
         <v>2.98</v>
       </c>
       <c r="K18" s="29" t="s">
@@ -1589,71 +1589,71 @@
         <v>-5</v>
       </c>
       <c r="G3" s="9">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="H3" s="9">
         <v>3.3</v>
       </c>
-      <c r="I3" s="12">
-        <v>4.95</v>
+      <c r="I3" s="8">
+        <v>9.9</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-5</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>-8</v>
       </c>
-      <c r="G4" s="13">
-        <v>0.17</v>
-      </c>
-      <c r="H4" s="13">
+      <c r="G4" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H4" s="12">
         <v>3</v>
       </c>
       <c r="I4" s="8">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <v>-8</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>-17</v>
       </c>
-      <c r="G5" s="16">
-        <v>0.25</v>
-      </c>
-      <c r="H5" s="16">
+      <c r="G5" s="15">
+        <v>2.25</v>
+      </c>
+      <c r="H5" s="15">
         <v>9</v>
       </c>
-      <c r="I5" s="8">
-        <v>36</v>
+      <c r="I5" s="18">
+        <v>4</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1710,7 +1710,7 @@
       <c r="H7" s="22">
         <v>4</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="18">
         <v>4.8</v>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       <c r="H9" s="28">
         <v>4.72</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="18">
         <v>2.98</v>
       </c>
     </row>
@@ -1792,13 +1792,13 @@
         <v>-44.22</v>
       </c>
       <c r="G10" s="33">
-        <v>5.5</v>
+        <v>7.25</v>
       </c>
       <c r="H10" s="33">
         <v>44.22</v>
       </c>
       <c r="I10" s="33">
-        <v>8.04</v>
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
